--- a/Книги/Рейтинг книг по темам — сверка 08.09.2026.xlsx
+++ b/Книги/Рейтинг книг по темам — сверка 08.09.2026.xlsx
@@ -734,10 +734,10 @@
         <v>56</v>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" t="n">
         <v>8</v>
@@ -4617,7 +4617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4776,6 +4776,63 @@
       <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Для строк, где текст обновлён с саммари до полного (Тайм-менеджмент №6, №7, №8), старый разбор/пометка «НЕ ПОЛНАЯ» помечены как устаревшие — сами разборы по полному тексту ещё не переписаны, это отдельная задача.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Обновление 09.09.2026 (вечер) — написаны разборы + сводный синтез:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Пользователь подтвердил легальное происхождение файлов из подозрительного источника (хэш+ID в имени) для 7 книг: Фрайд/Хенссон, Фридман (Пожиратели времени), Моран/Леннингтон, Феррис, Джонсон, Харфорд (Тайм-менеджмент, №6,7,8,9,12,28) и Кабейн «Харизма» (Общение, №49). По всем семи написаны полные 9-раздельные разборы с проверенными цитатами (файлы *.md, см. столбец «Разбор»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Дополнительно разобрана «Власть голоса» (Общение, №54) — чистый источник; в процессе работы определён автор (Жан Абитболь), поле «Автор» обновлено (было «—»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Строка №8 (12 недель в году): разбор написан по ЧИСТОМУ дублирующему файлу «12_недель_в_году.txt» (без хэш+ID суффикса), а не по подозрительному «Moran_...ALzsAw...» — тот файл остался неиспользованным.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Строка №15 (Тайм-менеджмент) помечена как дубль строки №7 (тот же Фридман/«Пожиратели времени») — не объединена физически (чтобы не сбить нумерацию), но разбор один, см. №7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ВАЖНАЯ КОРРЕКЦИЯ: строки №52 (Алекс Ром, «Ораторское мастерство за 30 дней») и №53 (Дейв Керпен, «Гений коммуникации») в «Общение» ранее числились Статус=«Есть» с комментарием «файл найден на диске». Техническая проверка (объём текста + маркеры ЛитРес) показала, что оба файла — это ознакомительные фрагменты ЛитРес (19-40 тыс. знаков, обрываются на «конец ознакомительного фрагмента»), НЕ полные книги. Статус исправлен на «Нет» у обеих строк. Разборы по ним не писались.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Собран сводный HTML-артефакт (синтез 257 техник из 12 книг: 30 межавторских пересечений, 11 прямых противоречий между авторами, 21 уникальная-но-важная техника, 27 целостных методик пошагово) — опубликован отдельной ссылкой, в эту таблицу не встроен.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>«Обзор» пересчитан: строки «Тайм-менеджмент» и «Общение, красноречие, голос» — по факту текущих статусов Есть/Нет (счётчик «Высокий приоритет» = общее число строк темы с Приоритет=Высокий, без учёта статуса — проверено соответствие исходным значениям 11 и 8 до правок).</t>
         </is>
       </c>
     </row>
@@ -18126,12 +18183,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Джейсон Фрайд — влиятельная книга о фокусе в работе | Ранее была только НЕ ПОЛНАЯ версия (саммари); теперь на диск добавлен ПОЛНЫЙ текст (Hensson_Ne-shodite-s-uma-na-rabote..., проверено — не фрагмент, ок. 164 тыс. знаков). текстовый файл — вероятно неавториз. источник (хэш+ID в имени); содержимое не используется без подтверждения легальности. [добавлено 09.09.2026]</t>
+          <t>Джейсон Фрайд — влиятельная книга о фокусе в работе | Ранее была только НЕ ПОЛНАЯ версия (саммари); теперь на диск добавлен ПОЛНЫЙ текст (Hensson_Ne-shodite-s-uma-na-rabote..., проверено — не фрагмент, ок. 164 тыс. знаков). текстовый файл — вероятно неавториз. источник (хэш+ID в имени); содержимое не используется без подтверждения легальности. [добавлено 09.09.2026] [разбор написан 09.09.2026] | Легальность копии подтверждена пользователем 09.09.2026, полный разбор написан — контент использован.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>ТЕКСТ ОБНОВЛЁН (полный) — см. комментарий, разбор ещё не переписан</t>
+          <t>РАЗОБРАНА (09.09.2026) — файл: фрайд_джейсон_не_сходите_с_ума_на_работе.md</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -18166,12 +18223,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Фридман — признанный эксперт по управленческому тайм-менеджменту | Ранее была только НЕ ПОЛНАЯ версия (саммари); теперь на диск добавлен ПОЛНЫЙ текст (Fridman_Pozhirateli-vremeni..., проверено — не фрагмент, ок. 370 тыс. знаков). Разбор по полному тексту ещё не написан — статус «РАЗОБРАНА» здесь означает не итоговый разбор, а факт наличия полного текста; актуализировать при следующем разборе книги. текстовый файл — вероятно неавториз. источник (хэш+ID в имени); содержимое не используется без подтверждения легальности. [добавлено 09.09.2026]</t>
+          <t>Фридман — признанный эксперт по управленческому тайм-менеджменту | Ранее была только НЕ ПОЛНАЯ версия (саммари); теперь на диск добавлен ПОЛНЫЙ текст (Fridman_Pozhirateli-vremeni..., проверено — не фрагмент, ок. 370 тыс. знаков). Разбор по полному тексту ещё не написан — статус «РАЗОБРАНА» здесь означает не итоговый разбор, а факт наличия полного текста; актуализировать при следующем разборе книги. текстовый файл — вероятно неавториз. источник (хэш+ID в имени); содержимое не используется без подтверждения легальности. [добавлено 09.09.2026] [разбор написан 09.09.2026] | Легальность копии подтверждена пользователем 09.09.2026, полный разбор написан — контент использован.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>ТЕКСТ ОБНОВЛЁН (полный) — см. комментарий, разбор ещё не переписан</t>
+          <t>РАЗОБРАНА (09.09.2026) — файл: фридман_александр_пожиратели_времени.md</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -18206,12 +18263,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Известная методология квартального планирования (было искажено: автор «16:02 книга»). Полную книгу найти не удалось — на диск добавлен только файл-саммари. [из скачанного] | На диске файл-саммари + аудио с Аудиокниги/ (источник — вероятно aiaudiobooks.org; содержимое не используется без подтверждения легальности). [сверка 08.09.2026] | Ранее считалось, что полную книгу найти не удалось (только саммари); теперь на диск добавлен ПОЛНЫЙ текст (Moran_12-nedel-v-godu..., проверено — не фрагмент, ок. 269 тыс. знаков). текстовый файл — вероятно неавториз. источник (хэш+ID в имени); содержимое не используется без подтверждения легальности. [добавлено 09.09.2026]</t>
+          <t>Известная методология квартального планирования (было искажено: автор «16:02 книга»). Полную книгу найти не удалось — на диск добавлен только файл-саммари. [из скачанного] | На диске файл-саммари + аудио с Аудиокниги/ (источник — вероятно aiaudiobooks.org; содержимое не используется без подтверждения легальности). [сверка 08.09.2026] | Ранее считалось, что полную книгу найти не удалось (только саммари); теперь на диск добавлен ПОЛНЫЙ текст (Moran_12-nedel-v-godu..., проверено — не фрагмент, ок. 269 тыс. знаков). текстовый файл — вероятно неавториз. источник (хэш+ID в имени); содержимое не используется без подтверждения легальности. [добавлено 09.09.2026] [разбор написан 09.09.2026] | Разбор написан по чистому файлу 12_недель_в_году.txt (не по хэш+ID дублю).</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>ТЕКСТ ОБНОВЛЁН (полный) — см. комментарий, разбор ещё не переписан</t>
+          <t>РАЗОБРАНА (09.09.2026) — файл: моран_леннингтон_12_недель_в_году.md</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -18246,7 +18303,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Тимоти Феррис — один из самых влиятельных бестселлеров по продуктивности (было искажено: автор «22:22 книга»). Это тот же «4-часовая рабочая неделя» из вашего нового списка. [из истории проекта] | Полный текст добавлен на диск, проверено — не фрагмент (ок. 508 тыс. знаков). текстовый файл — вероятно неавториз. источник (хэш+ID в имени); содержимое не используется без подтверждения легальности. [добавлено 09.09.2026]</t>
+          <t>Тимоти Феррис — один из самых влиятельных бестселлеров по продуктивности (было искажено: автор «22:22 книга»). Это тот же «4-часовая рабочая неделя» из вашего нового списка. [из истории проекта] | Полный текст добавлен на диск, проверено — не фрагмент (ок. 508 тыс. знаков). текстовый файл — вероятно неавториз. источник (хэш+ID в имени); содержимое не используется без подтверждения легальности. [добавлено 09.09.2026] [разбор написан 09.09.2026] | Легальность копии подтверждена пользователем 09.09.2026, полный разбор написан — контент использован.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>РАЗОБРАНА (09.09.2026) — файл: феррис_тим_как_работать_4_часа_в_неделю.md</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -18361,7 +18423,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Годовое планирование по неделям [ваш список] | Полный текст добавлен на диск, проверено — не фрагмент (ок. 255 тыс. знаков). текстовый файл — вероятно неавториз. источник (хэш+ID в имени); содержимое не используется без подтверждения легальности. [добавлено 09.09.2026]</t>
+          <t>Годовое планирование по неделям [ваш список] | Полный текст добавлен на диск, проверено — не фрагмент (ок. 255 тыс. знаков). текстовый файл — вероятно неавториз. источник (хэш+ID в имени); содержимое не используется без подтверждения легальности. [добавлено 09.09.2026] [разбор написан 09.09.2026] | Легальность копии подтверждена пользователем 09.09.2026, полный разбор написан — контент использован.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>РАЗОБРАНА (09.09.2026) — файл: джонсон_вик_52_понедельника.md</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -18466,12 +18533,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Фридман — поглотители времени [ваш список] | Похоже на дубль строки №7 (тот же автор/книга) — не объединено автоматически. Полный текст теперь тоже на диске. [добавлено 09.09.2026]</t>
+          <t>Фридман — поглотители времени [ваш список] | Похоже на дубль строки №7 (тот же автор/книга) — не объединено автоматически. Полный текст теперь тоже на диске. [добавлено 09.09.2026] [помечено как дубль 09.09.2026, не отдельный разбор]</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>ТЕКСТ ОБНОВЛЁН (полный) — см. комментарий, разбор ещё не переписан</t>
+          <t>ДУБЛЬ строки №7 (та же книга) — разбор см. в строке №7. Объединено 09.09.2026.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -18946,7 +19013,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>текст (Harford_Haos..., свободные_книги/) + аудио; текстовый файл — вероятно неавториз. источник (хэш+ID в имени); содержимое не используется без подтверждения легальности; аудио с Аудиокниги/ (источник — вероятно aiaudiobooks.org; содержимое не используется без подтверждения легальности). [сверка 08.09.2026]</t>
+          <t>текст (Harford_Haos..., свободные_книги/) + аудио; текстовый файл — вероятно неавториз. источник (хэш+ID в имени); содержимое не используется без подтверждения легальности; аудио с Аудиокниги/ (источник — вероятно aiaudiobooks.org; содержимое не используется без подтверждения легальности). [сверка 08.09.2026] [разбор написан 09.09.2026] | Легальность копии подтверждена пользователем 09.09.2026, полный разбор написан — контент использован.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>РАЗОБРАНА (09.09.2026) — файл: харфорд_тим_хаос.md</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -20757,7 +20829,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Харизма и влияние [ваш список] | текстовый файл — вероятно неавториз. источник (хэш+ID в имени); содержимое не используется без подтверждения легальности; плюс аудио с Аудиокниги/ (источник — вероятно aiaudiobooks.org; содержимое не используется без подтверждения легальности). [сверка 08.09.2026]</t>
+          <t>Харизма и влияние [ваш список] | текстовый файл — вероятно неавториз. источник (хэш+ID в имени); содержимое не используется без подтверждения легальности; плюс аудио с Аудиокниги/ (источник — вероятно aiaudiobooks.org; содержимое не используется без подтверждения легальности). [сверка 08.09.2026] [разбор написан 09.09.2026] | Легальность копии подтверждена пользователем 09.09.2026, полный разбор написан — контент использован.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>РАЗОБРАНА (09.09.2026) — файл: кабейн_оливия_фокс_харизма.md</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -20847,7 +20924,7 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Есть</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -20862,7 +20939,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Файл найден на диске. [из вашего списка «продажи, доп. книги» — распределено по разделам]</t>
+          <t>Файл найден на диске. [из вашего списка «продажи, доп. книги» — распределено по разделам] [ИСПРАВЛЕНО 09.09.2026: техническая проверка показала, что файл на диске — ознакомительный фрагмент ЛитРес (~20 тыс. знаков, обрывается на «конец ознакомительного фрагмента»), а не полная книга. Статус изменён с «Есть» на «Нет». Нужна полная версия для разбора.]</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -20882,7 +20959,7 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Есть</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -20897,7 +20974,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Файл найден на диске. [из вашего списка «продажи, доп. книги» — распределено по разделам]</t>
+          <t>Файл найден на диске. [из вашего списка «продажи, доп. книги» — распределено по разделам] [ИСПРАВЛЕНО 09.09.2026: техническая проверка показала, что файл на диске — ознакомительный фрагмент ЛитРес (~40 тыс. знаков, обрывается на «конец ознакомительного фрагмента»), а не полная книга. Статус изменён с «Есть» на «Нет». Нужна полная версия для разбора.]</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -20927,12 +21004,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Жан Абитболь</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>текст (Власть_голоса.txt, свободные_книги/) + аудио; аудио с Аудиокниги/ (источник — вероятно aiaudiobooks.org; содержимое не используется без подтверждения легальности). [сверка 08.09.2026]</t>
+          <t>текст (Власть_голоса.txt, свободные_книги/) + аудио; аудио с Аудиокниги/ (источник — вероятно aiaudiobooks.org; содержимое не используется без подтверждения легальности). [сверка 08.09.2026] [разбор написан 09.09.2026; автор определён по содержанию текста — Жан Абитболь, «Le Pouvoir de la Voix»]</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>РАЗОБРАНА (09.09.2026) — файл: власть_голоса.md</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
